--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>244324</v>
       </c>
       <c r="B2" t="n">
-        <v>78005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424312.3423570618</v>
+        <v>424312</v>
       </c>
       <c r="R2" t="n">
-        <v>6271042.548706956</v>
+        <v>6271043</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1997-03-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-03-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>244324</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>244324</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>244324</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>244324</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>79728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2021 artfynd.xlsx
+++ b/artfynd/A 37062-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>244324</v>
+        <v>66770497</v>
       </c>
       <c r="B2" t="n">
-        <v>79728</v>
+        <v>96447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor knopplav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mycobilimbia pilularis</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Körb.) Hafellner &amp; Türk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424312</v>
+        <v>424352</v>
       </c>
       <c r="R2" t="n">
-        <v>6271043</v>
+        <v>6271115</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-03-05</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-03-05</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rap till Sm Fl</t>
+          <t>På en levande bok</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,22 +773,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>På bok.</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Krister Wahlström</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -793,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66770587</v>
+        <v>66770604</v>
       </c>
       <c r="B3" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424306.6101821488</v>
+        <v>424315</v>
       </c>
       <c r="R3" t="n">
-        <v>6271092.230244642</v>
+        <v>6271095</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,19 +866,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,42 +900,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66770320</v>
+        <v>66770714</v>
       </c>
       <c r="B4" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -970,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424405.4263694515</v>
+        <v>424308</v>
       </c>
       <c r="R4" t="n">
-        <v>6271123.509569709</v>
+        <v>6271083</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,24 +978,14 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en levande ek</t>
+          <t>På en levande men klen bok</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66770311</v>
+        <v>66770801</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,25 +1023,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1089,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424312.3423570618</v>
+        <v>424318</v>
       </c>
       <c r="R5" t="n">
-        <v>6271042.548706956</v>
+        <v>6271096</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,23 +1090,18 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
         </is>
       </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
@@ -1161,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66770780</v>
+        <v>66770297</v>
       </c>
       <c r="B6" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1205,16 +1163,17 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424305.3879117112</v>
+        <v>424411</v>
       </c>
       <c r="R6" t="n">
-        <v>6271085.641734643</v>
+        <v>6271136</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,24 +1203,14 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en levande bok</t>
+          <t>På en levande bokhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,15 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66770453</v>
+        <v>66770338</v>
       </c>
       <c r="B7" t="n">
-        <v>78449</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,17 +1248,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6455</v>
+        <v>2667</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides s. lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1323,16 +1276,17 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424353.8916865598</v>
+        <v>424374</v>
       </c>
       <c r="R7" t="n">
-        <v>6271143.163228451</v>
+        <v>6271125</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,19 +1316,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1406,15 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66770733</v>
+        <v>66770343</v>
       </c>
       <c r="B8" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,17 +1370,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1457,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424302.6584712239</v>
+        <v>424373</v>
       </c>
       <c r="R8" t="n">
-        <v>6271087.343348295</v>
+        <v>6271125</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,19 +1429,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1534,15 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66770325</v>
+        <v>66770358</v>
       </c>
       <c r="B9" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,26 +1474,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1578,16 +1502,17 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424376.8307644597</v>
+        <v>424360</v>
       </c>
       <c r="R9" t="n">
-        <v>6271129.530998522</v>
+        <v>6271115</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1617,19 +1542,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1661,15 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66770748</v>
+        <v>66770372</v>
       </c>
       <c r="B10" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,26 +1587,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1705,16 +1615,17 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424302.6584712239</v>
+        <v>424364</v>
       </c>
       <c r="R10" t="n">
-        <v>6271087.343348295</v>
+        <v>6271126</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1744,19 +1655,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1788,15 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66770898</v>
+        <v>66770394</v>
       </c>
       <c r="B11" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,17 +1709,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1839,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424399.1391822093</v>
+        <v>424361</v>
       </c>
       <c r="R11" t="n">
-        <v>6271111.503225539</v>
+        <v>6271117</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1872,24 +1768,14 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en levande bok</t>
+          <t>På en levande bok. 300 är rätt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,15 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66770575</v>
+        <v>66770407</v>
       </c>
       <c r="B12" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,17 +1822,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1967,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424307.2707450239</v>
+        <v>424358</v>
       </c>
       <c r="R12" t="n">
-        <v>6271098.277958347</v>
+        <v>6271106</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2000,19 +1881,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2044,15 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66770297</v>
+        <v>66770416</v>
       </c>
       <c r="B13" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,17 +1935,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2095,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424411.1617082485</v>
+        <v>424352</v>
       </c>
       <c r="R13" t="n">
-        <v>6271135.52578071</v>
+        <v>6271118</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2128,24 +1994,14 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en levande bokhögstubbe</t>
+          <t>På en levande bok</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,15 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66770465</v>
+        <v>66770421</v>
       </c>
       <c r="B14" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,26 +2039,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2216,16 +2067,17 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Agghult, Traryd, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424353.8916865598</v>
+        <v>424352</v>
       </c>
       <c r="R14" t="n">
-        <v>6271143.163228451</v>
+        <v>6271132</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2255,24 +2107,14 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en levande bok</t>
+          <t>På en högstubbe av bok</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2302,12 +2144,7 @@
         <v>66770467</v>
       </c>
       <c r="B15" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,12 +2161,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2350,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424353.8916865598</v>
+        <v>424354</v>
       </c>
       <c r="R15" t="n">
-        <v>6271143.163228451</v>
+        <v>6271143</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2383,19 +2220,9 @@
           <t>2017-07-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2424,6 +2251,3338 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>66770474</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>424336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6271131</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en död bokhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>66770492</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>424352</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6271115</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>66770563</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>424337</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6271105</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>66770575</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>424307</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6271098</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>66770612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>424315</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6271095</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>66770733</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>424303</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6271087</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>66770795</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>424318</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6271096</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>66770898</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>424399</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6271112</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>66770378</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6455</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>424364</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6271126</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>66770428</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6455</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>424352</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6271132</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en högstubbe av bok</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>66770453</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6455</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>424354</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6271143</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>66770487</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6455</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>424352</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6271115</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>66770320</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>424405</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6271124</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en levande ek</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>66770325</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>424377</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6271130</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>66770330</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>424374</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6271125</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>66770348</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>424373</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6271125</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>66770365</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>424360</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6271115</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>66770384</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>424364</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6271126</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>66770465</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>424354</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6271143</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>66770481</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>424341</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6271119</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en levande ek</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>66770587</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>424307</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6271092</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>66770592</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>424309</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6271088</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>66770748</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>424303</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6271087</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>66770761</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>424308</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6271085</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>66770780</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>424305</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6271086</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>66770813</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>424325</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6271064</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>66770818</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>424332</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6271063</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>66770826</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>424339</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6271078</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>66770832</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>424333</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6271075</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>66770836</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Agghult, Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>424333</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6271081</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Traryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
